--- a/西笑院HP作業ログ_完全版.xlsx
+++ b/西笑院HP作業ログ_完全版.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2287,6 +2287,119 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>戻し方: git checkout v2.5 -- index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>アクセス：カーナビ注意書き追加（裏手案内・Googleマップ推奨）</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>アクセス：駐車場を東第一（16台）・西第二（7台）に正式名称更新</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>アクセス：駐車場写真をIMG_4228（東第一駐車場）に差し替え</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>index.html・IMG_4228.jpeg</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>駐車場案内図（parking_map.png）をPython/Pillowで作成。CAD風・凡例・北矢印付き。サイト未掲載・掲載場所検討中</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>parking_map.png</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>掲載場所未定</t>
         </is>
       </c>
     </row>

--- a/西笑院HP作業ログ_完全版.xlsx
+++ b/西笑院HP作業ログ_完全版.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2400,6 +2400,92 @@
       <c r="G65" t="inlineStr">
         <is>
           <t>掲載場所未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ギャラリー：赤門キャプションに伊勢湾台風エピソード追加。「同じ時を刻む赤門と松」はタイトルのみ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SEO：タイトルを「【公式】西笑院｜創建620年を越える八王子の禅寺」に変更</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ヒーロー：庭園追加試みるも表示されず（MPO形式・日本語パス問題）→元の4枚に戻した</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>index.html・garden.jpeg</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>garden.jpegはルートに残存・未使用</t>
         </is>
       </c>
     </row>
